--- a/output/pdf_financials_xlsx/KLN.xlsx
+++ b/output/pdf_financials_xlsx/KLN.xlsx
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.003209</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.003209</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.514</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.514</v>
       </c>
     </row>
     <row r="93">
@@ -3848,7 +3848,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4384,7 +4388,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>1.003209</v>
       </c>

--- a/output/pdf_financials_xlsx/KLN.xlsx
+++ b/output/pdf_financials_xlsx/KLN.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.402177</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.139409</v>
+        <v>5.1833</v>
       </c>
     </row>
     <row r="11">
@@ -1190,13 +1190,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000378</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.379414</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.318861</v>
       </c>
     </row>
     <row r="35">
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000378</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.379414</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.318861</v>
       </c>
     </row>
     <row r="37">
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.535331</v>
+        <v>5.155917</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.771987</v>
+        <v>4.453126</v>
       </c>
     </row>
     <row r="49">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">

--- a/output/pdf_financials_xlsx/KLN.xlsx
+++ b/output/pdf_financials_xlsx/KLN.xlsx
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.02287</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.161342</v>
       </c>
     </row>
     <row r="8">
@@ -6270,7 +6270,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
